--- a/05-rockledge-benefits-ai-governance/artifacts/ai_system_inventory.xlsx
+++ b/05-rockledge-benefits-ai-governance/artifacts/ai_system_inventory.xlsx
@@ -593,10 +593,11 @@
     <row r="2" ht="15" customHeight="1" s="13">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>Framework basis: NIST AI RMF 1.0 (Map), EU AI Act as amended by Regulation (EU) 2026/1744 (Digital Omnibus on AI, in force 27 July 2026), ISO/IEC 42001 A.4 | Inventory date: 2026-08-05 | Fictional organization. Created for portfolio demonstration purposes.</t>
-        </is>
-      </c>
-    </row>
+          <t>Framework basis: NIST AI RMF 1.0 (Map), EU AI Act as amended by Regulation (EU) 2026/1744 (Digital Omnibus on AI, in force 27 July 2026), ISO/IEC 42001 A.4 | Inventory date: 2026-07-29 | Fictional organization. Created for portfolio demonstration purposes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="23.85" customHeight="1" s="13">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -1743,6 +1744,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="13">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -1821,6 +1823,7 @@
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="13">
       <c r="A12" s="16" t="inlineStr">
         <is>
@@ -1866,6 +1869,7 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="15" customHeight="1" s="13">
       <c r="A17" s="18" t="inlineStr">
         <is>
@@ -1926,6 +1930,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="35.05" customHeight="1" s="13">
       <c r="A3" s="20" t="inlineStr">
         <is>

--- a/05-rockledge-benefits-ai-governance/artifacts/ai_system_inventory.xlsx
+++ b/05-rockledge-benefits-ai-governance/artifacts/ai_system_inventory.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="P5" s="17" t="inlineStr">
         <is>
-          <t>CONTESTED. Annex III(5)(a) covers essential PUBLIC assistance benefits by public authorities — Rockledge is a private administrator. Annex III(5)(c) covers risk assessment and pricing for life/health insurance — this is claims adjudication, not pricing. Neither category fits cleanly. Treated as high-risk pending counsel determination; see Risk AIR-004 for both classification outcomes.</t>
+          <t>CONTESTED. Annex III(5)(a) covers systems used by or on behalf of public authorities for essential public assistance benefits — Rockledge is a private administrator, and the open question is whether it acts on behalf of a public authority. Annex III(5)(c) covers risk assessment and pricing for life/health insurance — this is claims adjudication, not pricing. Neither category fits cleanly. Treated as high-risk pending counsel determination; see Risk AIR-004 for both classification outcomes.</t>
         </is>
       </c>
       <c r="Q5" s="17" t="inlineStr">

--- a/05-rockledge-benefits-ai-governance/artifacts/ai_system_inventory.xlsx
+++ b/05-rockledge-benefits-ai-governance/artifacts/ai_system_inventory.xlsx
@@ -705,7 +705,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="113.4" customHeight="1" s="13">
+    <row r="5" ht="157" customHeight="1" s="13">
       <c r="A5" s="17" t="inlineStr">
         <is>
           <t>AI-001</t>
